--- a/output/pdf_financials_xlsx/CANU.xlsx
+++ b/output/pdf_financials_xlsx/CANU.xlsx
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.071865</v>
+        <v>-0.071865</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.147068</v>
+        <v>-0.147068</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CANU.xlsx
+++ b/output/pdf_financials_xlsx/CANU.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.061062</v>
+        <v>0.222514</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.362911</v>
+        <v>1.442439</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.07971200000000001</v>
+        <v>0.124038</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.196238</v>
+        <v>0.273562</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.061062</v>
+        <v>-0.222514</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.362911</v>
+        <v>-1.442439</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.07971200000000001</v>
+        <v>-0.124038</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.196238</v>
+        <v>-0.273562</v>
       </c>
     </row>
     <row r="12">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000299</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.222215</v>
+        <v>-0.222514</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.432439</v>
+        <v>-1.442439</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.078704</v>
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.222215</v>
+        <v>-0.222514</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.432439</v>
+        <v>-1.442439</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.078704</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.06321300000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.20154</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09982000000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.967462</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.06321300000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.20154</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.09982000000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.967462</v>
       </c>
     </row>
     <row r="37">
@@ -1349,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09982000000000001</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.9680609999999999</v>
+        <v>0.000599</v>
       </c>
     </row>
     <row r="49">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -6200,20 +6200,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.222514</v>
+        <v>0.222514</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-1.442439</v>
+        <v>1.442439</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.124038</v>
+        <v>0.124038</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>-0.273562</v>
+        <v>0.273562</v>
       </c>
     </row>
     <row r="87">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">

--- a/output/pdf_financials_xlsx/CANU.xlsx
+++ b/output/pdf_financials_xlsx/CANU.xlsx
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.00144</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.041145</v>
+        <v>-0.039705</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.083161</v>
@@ -5512,7 +5512,11 @@
           <t>Increase in HST/GST receivable</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.00144</v>
       </c>
